--- a/Template Import/Templates ceced  Draft.xlsx
+++ b/Template Import/Templates ceced  Draft.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80D4886-5D8B-4486-B309-21A3F2786B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6593D236-4D73-4906-9924-E27E6CE2E6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" activeTab="1" xr2:uid="{09B12BF0-3879-48C9-832D-2E48D6CE9129}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{09B12BF0-3879-48C9-832D-2E48D6CE9129}"/>
   </bookViews>
   <sheets>
     <sheet name="Templates ceced  h" sheetId="1" r:id="rId1"/>
     <sheet name="Templates ceced  l" sheetId="2" r:id="rId2"/>
+    <sheet name="VENDOR+PRODUCT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="104">
   <si>
     <t>JdtNum</t>
   </si>
@@ -115,13 +116,250 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRODUCT </t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>604.01.00.01</t>
+  </si>
+  <si>
+    <t>604.01.00.02</t>
+  </si>
+  <si>
+    <t>604.01.00.03</t>
+  </si>
+  <si>
+    <t>604.01.00.04</t>
+  </si>
+  <si>
+    <t>604.01.00.05</t>
+  </si>
+  <si>
+    <t>604.01.00.06</t>
+  </si>
+  <si>
+    <t>604.01.00.07</t>
+  </si>
+  <si>
+    <t>604.01.00.08</t>
+  </si>
+  <si>
+    <t>604.01.00.09</t>
+  </si>
+  <si>
+    <t>604.01.00.10</t>
+  </si>
+  <si>
+    <t>604.01.00.11</t>
+  </si>
+  <si>
+    <t>604.01.00.12</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Compulsory</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Voluntary</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Credit Life</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Fire</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Health</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Marine</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ MISC</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ PA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ TA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Property</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ Engineering</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ພິເສດ IAR</t>
+  </si>
+  <si>
+    <t>Facutative</t>
+  </si>
+  <si>
+    <t>Treaty</t>
+  </si>
+  <si>
+    <t>604.02.00.01</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Compulsory</t>
+  </si>
+  <si>
+    <t>604.02.00.02</t>
+  </si>
+  <si>
+    <t>604.02.00.03</t>
+  </si>
+  <si>
+    <t>604.02.00.04</t>
+  </si>
+  <si>
+    <t>604.02.00.05</t>
+  </si>
+  <si>
+    <t>604.02.00.06</t>
+  </si>
+  <si>
+    <t>604.02.00.07</t>
+  </si>
+  <si>
+    <t>604.02.00.08</t>
+  </si>
+  <si>
+    <t>604.02.00.09</t>
+  </si>
+  <si>
+    <t>604.02.00.10</t>
+  </si>
+  <si>
+    <t>604.02.00.11</t>
+  </si>
+  <si>
+    <t>604.02.00.12</t>
+  </si>
+  <si>
+    <t>604.03.00.01</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Compulsory</t>
+  </si>
+  <si>
+    <t>604.03.00.02</t>
+  </si>
+  <si>
+    <t>604.03.00.03</t>
+  </si>
+  <si>
+    <t>604.03.00.04</t>
+  </si>
+  <si>
+    <t>604.03.00.05</t>
+  </si>
+  <si>
+    <t>604.03.00.06</t>
+  </si>
+  <si>
+    <t>604.03.00.07</t>
+  </si>
+  <si>
+    <t>604.03.00.08</t>
+  </si>
+  <si>
+    <t>604.03.00.09</t>
+  </si>
+  <si>
+    <t>604.03.00.10</t>
+  </si>
+  <si>
+    <t>604.03.00.11</t>
+  </si>
+  <si>
+    <t>604.03.00.12</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Voluntary</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Credit Life</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Fire</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Health</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Marine</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ MISC</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ PA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ TA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Property</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ Engineering</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ອື່ນໆ IAR</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Voluntary</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Credit Life</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Fire</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Health</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Marine</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ MISC</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ PA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ TA</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Property</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ Engineering</t>
+  </si>
+  <si>
+    <t>ລາຍຈ່າຍປະກັນໄພຕໍ່ຕາມພັນທະ IAR</t>
+  </si>
+  <si>
+    <t>ລູກຄ້າສັນຍາປະກັນໄພຕໍ່-ພິເສດ</t>
+  </si>
+  <si>
+    <t>ລູກຄ້າສັນຍາປະກັນໄພຕໍ່-ພັນທະ</t>
+  </si>
+  <si>
+    <t>ລູກຄ້າສັນຍາປະກັນໄພຕໍ່-ອື່ນໆ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +374,24 @@
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Phetsarath OT"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -171,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -192,6 +448,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,13 +793,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9863803F-08DA-42C7-A3B4-5B7E2B44D168}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" customWidth="1"/>
-    <col min="2" max="2" width="12.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="12.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,7 +819,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -598,17 +864,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F404564A-F0AA-4B8E-9CB9-959B600F0A64}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.9140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -634,7 +900,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -660,7 +926,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -682,7 +948,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -704,7 +970,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -726,7 +992,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -751,4 +1017,344 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA1D912-3CEC-412C-B71C-0E945E9AC4D1}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="12.08203125" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.9140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="12">
+        <v>408.01</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="12">
+        <v>408.02</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="12">
+        <v>408.03</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E31" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>